--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R9" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R10" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B9" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,64 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>57016</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,45 +1755,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>57016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R9" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R10" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,45 +1648,64 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>57016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R11" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,64 +1774,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>80285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R12" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130358340</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>130359237</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>130358664</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>78190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>79773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R5" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>79770</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R6" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,12 +1203,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
         <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>92323</v>
+        <v>92326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,12 +1422,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
         <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
         <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,76 +1636,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>57016</v>
+        <v>80288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,57 +1743,76 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>57016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,22 +1869,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356809</v>
+        <v>130359609</v>
       </c>
       <c r="B13" t="n">
-        <v>83150</v>
+        <v>80289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485662</v>
+        <v>485646</v>
       </c>
       <c r="R13" t="n">
-        <v>6939425</v>
+        <v>6939616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1976,22 +1976,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130359609</v>
+        <v>130356809</v>
       </c>
       <c r="B14" t="n">
-        <v>80286</v>
+        <v>83153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485646</v>
+        <v>485662</v>
       </c>
       <c r="R14" t="n">
-        <v>6939616</v>
+        <v>6939425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2083,12 +2083,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
         <v>130356367</v>
       </c>
       <c r="B15" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,12 +2190,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
         <v>130356648</v>
       </c>
       <c r="B16" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,12 +2297,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2312,7 +2312,7 @@
         <v>130358621</v>
       </c>
       <c r="B17" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>130356078</v>
       </c>
       <c r="B18" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,12 +2511,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2526,7 +2526,7 @@
         <v>130356107</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,12 +2618,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
         <v>130356201</v>
       </c>
       <c r="B20" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,12 +2725,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
         <v>130358819</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,12 +2832,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2847,7 +2847,7 @@
         <v>130356560</v>
       </c>
       <c r="B22" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,12 +2939,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2954,7 +2954,7 @@
         <v>130356644</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,15 +3046,1425 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Skogsutskottet Utskottet</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130609237</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>485567</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6939406</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130607800</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>485525</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6939315</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130609563</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80314</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>485409</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6939407</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130608442</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>485650</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6939249</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130607296</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79241</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>485415</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6939350</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130608573</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80314</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>485661</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6939262</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130607874</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80314</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>485546</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6939308</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130607970</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80314</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>485558</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6939298</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130607960</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>760</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>485558</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6939298</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130608723</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80314</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>485644</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6939283</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grankvistar</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130606943</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58011</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>485317</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6939367</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130608518</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91721</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>485649</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6939253</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130609721</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>485397</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6939386</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130358340</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130359237</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130358664</v>
       </c>
       <c r="B4" t="n">
-        <v>78190</v>
+        <v>78216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>92326</v>
+        <v>92352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130359609</v>
+        <v>130356367</v>
       </c>
       <c r="B13" t="n">
-        <v>80289</v>
+        <v>78966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485646</v>
+        <v>485434</v>
       </c>
       <c r="R13" t="n">
-        <v>6939616</v>
+        <v>6939341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,7 +1991,7 @@
         <v>130356809</v>
       </c>
       <c r="B14" t="n">
-        <v>83153</v>
+        <v>83179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356367</v>
+        <v>130359609</v>
       </c>
       <c r="B15" t="n">
-        <v>78940</v>
+        <v>80315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485434</v>
+        <v>485646</v>
       </c>
       <c r="R15" t="n">
-        <v>6939341</v>
+        <v>6939616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2205,7 @@
         <v>130356648</v>
       </c>
       <c r="B16" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130358621</v>
       </c>
       <c r="B17" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130356078</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>130356107</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>130356201</v>
       </c>
       <c r="B20" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>130358819</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>130356560</v>
       </c>
       <c r="B22" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130356644</v>
       </c>
       <c r="B23" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130606943</v>
+        <v>130609721</v>
       </c>
       <c r="B34" t="n">
-        <v>58011</v>
+        <v>80315</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,48 +4144,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485317</v>
+        <v>485397</v>
       </c>
       <c r="R34" t="n">
-        <v>6939367</v>
+        <v>6939386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4227,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4361,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130609721</v>
+        <v>130606943</v>
       </c>
       <c r="B36" t="n">
-        <v>80315</v>
+        <v>58011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,34 +4358,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485397</v>
+        <v>485317</v>
       </c>
       <c r="R36" t="n">
-        <v>6939386</v>
+        <v>6939367</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356367</v>
+        <v>130359609</v>
       </c>
       <c r="B13" t="n">
-        <v>78966</v>
+        <v>80315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485434</v>
+        <v>485646</v>
       </c>
       <c r="R13" t="n">
-        <v>6939341</v>
+        <v>6939616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130359609</v>
+        <v>130356367</v>
       </c>
       <c r="B15" t="n">
-        <v>80315</v>
+        <v>78966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485646</v>
+        <v>485434</v>
       </c>
       <c r="R15" t="n">
-        <v>6939616</v>
+        <v>6939341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>92352</v>
+        <v>92353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B9" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,45 +1648,64 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>57042</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R11" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,64 +1774,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B12" t="n">
-        <v>57042</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R12" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130359609</v>
+        <v>130356809</v>
       </c>
       <c r="B13" t="n">
-        <v>80315</v>
+        <v>83180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485646</v>
+        <v>485662</v>
       </c>
       <c r="R13" t="n">
-        <v>6939616</v>
+        <v>6939425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130356809</v>
+        <v>130359609</v>
       </c>
       <c r="B14" t="n">
-        <v>83179</v>
+        <v>80315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485662</v>
+        <v>485646</v>
       </c>
       <c r="R14" t="n">
-        <v>6939425</v>
+        <v>6939616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92352</v>
+        <v>92353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>130608518</v>
       </c>
       <c r="B35" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R5" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R6" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>92353</v>
+        <v>92354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R9" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R10" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,64 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>57042</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,45 +1755,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>57042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,7 +1884,7 @@
         <v>130356809</v>
       </c>
       <c r="B13" t="n">
-        <v>83180</v>
+        <v>83181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92353</v>
+        <v>92354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130609721</v>
+        <v>130606943</v>
       </c>
       <c r="B34" t="n">
-        <v>80315</v>
+        <v>58011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,34 +4144,48 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485397</v>
+        <v>485317</v>
       </c>
       <c r="R34" t="n">
-        <v>6939386</v>
+        <v>6939367</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4203,7 +4217,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4227,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,32 +4254,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B35" t="n">
-        <v>91722</v>
+        <v>80315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4275,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R35" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4310,7 +4324,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4320,7 +4334,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,59 +4361,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130606943</v>
+        <v>130608518</v>
       </c>
       <c r="B36" t="n">
-        <v>58011</v>
+        <v>91723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485317</v>
+        <v>485649</v>
       </c>
       <c r="R36" t="n">
-        <v>6939367</v>
+        <v>6939253</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130358340</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130359237</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130358664</v>
       </c>
       <c r="B4" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130356714</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>130356032</v>
       </c>
       <c r="B6" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>92354</v>
+        <v>92356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,45 +1648,64 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R11" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,64 +1774,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B12" t="n">
-        <v>57042</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R12" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356809</v>
+        <v>130356367</v>
       </c>
       <c r="B13" t="n">
-        <v>83181</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485662</v>
+        <v>485434</v>
       </c>
       <c r="R13" t="n">
-        <v>6939425</v>
+        <v>6939341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,7 +1991,7 @@
         <v>130359609</v>
       </c>
       <c r="B14" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B15" t="n">
-        <v>78966</v>
+        <v>83183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R15" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2205,7 @@
         <v>130356648</v>
       </c>
       <c r="B16" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130358621</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130356078</v>
       </c>
       <c r="B18" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>130356107</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>130356201</v>
       </c>
       <c r="B20" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>130358819</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>130356560</v>
       </c>
       <c r="B22" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130356644</v>
       </c>
       <c r="B23" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130609237</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>130607800</v>
       </c>
       <c r="B25" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>130609563</v>
       </c>
       <c r="B26" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>130608442</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130607296</v>
       </c>
       <c r="B28" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>130608573</v>
       </c>
       <c r="B29" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>130607874</v>
       </c>
       <c r="B30" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>130607970</v>
       </c>
       <c r="B31" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92354</v>
+        <v>92356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>130608723</v>
       </c>
       <c r="B33" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>130606943</v>
       </c>
       <c r="B34" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>130609721</v>
       </c>
       <c r="B35" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130608518</v>
       </c>
       <c r="B36" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>79801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R5" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>79801</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R6" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130356174</v>
+        <v>130359584</v>
       </c>
       <c r="B8" t="n">
-        <v>92356</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485386</v>
+        <v>485661</v>
       </c>
       <c r="R8" t="n">
-        <v>6939403</v>
+        <v>6939645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130356174</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>92360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485386</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>83183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R13" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130359609</v>
+        <v>130356367</v>
       </c>
       <c r="B14" t="n">
-        <v>80317</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485646</v>
+        <v>485434</v>
       </c>
       <c r="R14" t="n">
-        <v>6939616</v>
+        <v>6939341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356809</v>
+        <v>130359609</v>
       </c>
       <c r="B15" t="n">
-        <v>83183</v>
+        <v>80317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485662</v>
+        <v>485646</v>
       </c>
       <c r="R15" t="n">
-        <v>6939425</v>
+        <v>6939616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92356</v>
+        <v>92360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130606943</v>
+        <v>130609721</v>
       </c>
       <c r="B34" t="n">
-        <v>58013</v>
+        <v>80317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,48 +4144,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485317</v>
+        <v>485397</v>
       </c>
       <c r="R34" t="n">
-        <v>6939367</v>
+        <v>6939386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4227,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,32 +4240,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130609721</v>
+        <v>130608518</v>
       </c>
       <c r="B35" t="n">
-        <v>80317</v>
+        <v>91725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4289,10 +4275,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485397</v>
+        <v>485649</v>
       </c>
       <c r="R35" t="n">
-        <v>6939386</v>
+        <v>6939253</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4310,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4334,7 +4320,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4361,45 +4347,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130608518</v>
+        <v>130606943</v>
       </c>
       <c r="B36" t="n">
-        <v>91725</v>
+        <v>58013</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485649</v>
+        <v>485317</v>
       </c>
       <c r="R36" t="n">
-        <v>6939253</v>
+        <v>6939367</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B5" t="n">
-        <v>79801</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R5" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>79801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R6" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130359584</v>
+        <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>92360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485661</v>
+        <v>485386</v>
       </c>
       <c r="R8" t="n">
-        <v>6939645</v>
+        <v>6939403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R9" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356174</v>
+        <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>92360</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485386</v>
+        <v>485464</v>
       </c>
       <c r="R10" t="n">
-        <v>6939403</v>
+        <v>6939338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356809</v>
+        <v>130356367</v>
       </c>
       <c r="B13" t="n">
-        <v>83183</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485662</v>
+        <v>485434</v>
       </c>
       <c r="R13" t="n">
-        <v>6939425</v>
+        <v>6939341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>83183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R14" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>79801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R5" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>79801</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R6" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130356174</v>
+        <v>130359584</v>
       </c>
       <c r="B8" t="n">
-        <v>92360</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485386</v>
+        <v>485661</v>
       </c>
       <c r="R8" t="n">
-        <v>6939403</v>
+        <v>6939645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130356174</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>92360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485386</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,64 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>57044</v>
+        <v>80316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,45 +1755,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356367</v>
+        <v>130359609</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>80317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485434</v>
+        <v>485646</v>
       </c>
       <c r="R13" t="n">
-        <v>6939341</v>
+        <v>6939616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130359609</v>
+        <v>130356367</v>
       </c>
       <c r="B15" t="n">
-        <v>80317</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485646</v>
+        <v>485434</v>
       </c>
       <c r="R15" t="n">
-        <v>6939616</v>
+        <v>6939341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130609721</v>
+        <v>130606943</v>
       </c>
       <c r="B34" t="n">
-        <v>80317</v>
+        <v>58013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,34 +4144,48 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485397</v>
+        <v>485317</v>
       </c>
       <c r="R34" t="n">
-        <v>6939386</v>
+        <v>6939367</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4203,7 +4217,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4227,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4347,10 +4361,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130606943</v>
+        <v>130609721</v>
       </c>
       <c r="B36" t="n">
-        <v>58013</v>
+        <v>80317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,48 +4372,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485317</v>
+        <v>485397</v>
       </c>
       <c r="R36" t="n">
-        <v>6939367</v>
+        <v>6939386</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B5" t="n">
-        <v>79801</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R5" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>79801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R6" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130359584</v>
+        <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>92360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485661</v>
+        <v>485386</v>
       </c>
       <c r="R8" t="n">
-        <v>6939645</v>
+        <v>6939403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R9" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356174</v>
+        <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>92360</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485386</v>
+        <v>485464</v>
       </c>
       <c r="R10" t="n">
-        <v>6939403</v>
+        <v>6939338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4254,32 +4254,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B35" t="n">
-        <v>91725</v>
+        <v>80317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R35" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4361,32 +4361,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130609721</v>
+        <v>130608518</v>
       </c>
       <c r="B36" t="n">
-        <v>80317</v>
+        <v>91725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485397</v>
+        <v>485649</v>
       </c>
       <c r="R36" t="n">
-        <v>6939386</v>
+        <v>6939253</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130358340</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130359237</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130358664</v>
       </c>
       <c r="B4" t="n">
-        <v>78218</v>
+        <v>78226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>79809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R5" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>79801</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R6" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83057</v>
+        <v>83065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>92360</v>
+        <v>92373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,45 +1648,64 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B11" t="n">
-        <v>80316</v>
+        <v>57052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R11" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,64 +1774,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B12" t="n">
-        <v>57044</v>
+        <v>80324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R12" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,7 +1884,7 @@
         <v>130359609</v>
       </c>
       <c r="B13" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>130356809</v>
       </c>
       <c r="B14" t="n">
-        <v>83183</v>
+        <v>83191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>130356367</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>130356648</v>
       </c>
       <c r="B16" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130358621</v>
       </c>
       <c r="B17" t="n">
-        <v>78969</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130356078</v>
       </c>
       <c r="B18" t="n">
-        <v>79801</v>
+        <v>79809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>130356107</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>130356201</v>
       </c>
       <c r="B20" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>130358819</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>130356560</v>
       </c>
       <c r="B22" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130356644</v>
       </c>
       <c r="B23" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130609237</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>130607800</v>
       </c>
       <c r="B25" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>130609563</v>
       </c>
       <c r="B26" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>130608442</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130607296</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>79251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>130608573</v>
       </c>
       <c r="B29" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>130607874</v>
       </c>
       <c r="B30" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>130607970</v>
       </c>
       <c r="B31" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92360</v>
+        <v>92373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>130608723</v>
       </c>
       <c r="B33" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,59 +4133,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130606943</v>
+        <v>130608518</v>
       </c>
       <c r="B34" t="n">
-        <v>58013</v>
+        <v>91737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485317</v>
+        <v>485649</v>
       </c>
       <c r="R34" t="n">
-        <v>6939367</v>
+        <v>6939253</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4227,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130609721</v>
+        <v>130606943</v>
       </c>
       <c r="B35" t="n">
-        <v>80317</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4265,34 +4251,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485397</v>
+        <v>485317</v>
       </c>
       <c r="R35" t="n">
-        <v>6939386</v>
+        <v>6939367</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4361,32 +4361,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B36" t="n">
-        <v>91725</v>
+        <v>80325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R36" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130358340</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130359237</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130358664</v>
       </c>
       <c r="B4" t="n">
-        <v>78226</v>
+        <v>78227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>79809</v>
+        <v>79810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83065</v>
+        <v>83066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130356174</v>
+        <v>130359584</v>
       </c>
       <c r="B8" t="n">
-        <v>92373</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485386</v>
+        <v>485661</v>
       </c>
       <c r="R8" t="n">
-        <v>6939403</v>
+        <v>6939645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B9" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130356174</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>92374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485386</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1651,7 @@
         <v>130356521</v>
       </c>
       <c r="B11" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>130356574</v>
       </c>
       <c r="B12" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130359609</v>
+        <v>130356367</v>
       </c>
       <c r="B13" t="n">
-        <v>80325</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485646</v>
+        <v>485434</v>
       </c>
       <c r="R13" t="n">
-        <v>6939616</v>
+        <v>6939341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130356809</v>
+        <v>130359609</v>
       </c>
       <c r="B14" t="n">
-        <v>83191</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485662</v>
+        <v>485646</v>
       </c>
       <c r="R14" t="n">
-        <v>6939425</v>
+        <v>6939616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B15" t="n">
-        <v>78976</v>
+        <v>83192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R15" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2205,7 @@
         <v>130356648</v>
       </c>
       <c r="B16" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130358621</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130356078</v>
       </c>
       <c r="B18" t="n">
-        <v>79809</v>
+        <v>79810</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>130356107</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>130356201</v>
       </c>
       <c r="B20" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>130358819</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>130356560</v>
       </c>
       <c r="B22" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130356644</v>
       </c>
       <c r="B23" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130609237</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>130607800</v>
       </c>
       <c r="B25" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>130609563</v>
       </c>
       <c r="B26" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>130608442</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130607296</v>
       </c>
       <c r="B28" t="n">
-        <v>79251</v>
+        <v>79252</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>130608573</v>
       </c>
       <c r="B29" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>130607874</v>
       </c>
       <c r="B30" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>130607970</v>
       </c>
       <c r="B31" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>130608723</v>
       </c>
       <c r="B33" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,32 +4133,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B34" t="n">
-        <v>91737</v>
+        <v>80326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R34" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,59 +4240,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130606943</v>
+        <v>130608518</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>91738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485317</v>
+        <v>485649</v>
       </c>
       <c r="R35" t="n">
-        <v>6939367</v>
+        <v>6939253</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4310,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4334,7 +4320,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4361,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130609721</v>
+        <v>130606943</v>
       </c>
       <c r="B36" t="n">
-        <v>80325</v>
+        <v>58022</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,34 +4358,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485397</v>
+        <v>485317</v>
       </c>
       <c r="R36" t="n">
-        <v>6939386</v>
+        <v>6939367</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130358340</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130359237</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130358664</v>
       </c>
       <c r="B4" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130356032</v>
       </c>
       <c r="B5" t="n">
-        <v>79810</v>
+        <v>79811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130356714</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>83066</v>
+        <v>83067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130359584</v>
+        <v>130356174</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>92375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485661</v>
+        <v>485386</v>
       </c>
       <c r="R8" t="n">
-        <v>6939645</v>
+        <v>6939403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130356421</v>
+        <v>130359584</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485464</v>
+        <v>485661</v>
       </c>
       <c r="R9" t="n">
-        <v>6939338</v>
+        <v>6939645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356174</v>
+        <v>130356421</v>
       </c>
       <c r="B10" t="n">
-        <v>92374</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485386</v>
+        <v>485464</v>
       </c>
       <c r="R10" t="n">
-        <v>6939403</v>
+        <v>6939338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,64 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,45 +1755,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>80325</v>
+        <v>57053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>83193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R13" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130359609</v>
+        <v>130356367</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>78978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485646</v>
+        <v>485434</v>
       </c>
       <c r="R14" t="n">
-        <v>6939616</v>
+        <v>6939341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356809</v>
+        <v>130359609</v>
       </c>
       <c r="B15" t="n">
-        <v>83192</v>
+        <v>80327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485662</v>
+        <v>485646</v>
       </c>
       <c r="R15" t="n">
-        <v>6939425</v>
+        <v>6939616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2205,7 @@
         <v>130356648</v>
       </c>
       <c r="B16" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130358621</v>
       </c>
       <c r="B17" t="n">
-        <v>78978</v>
+        <v>78979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130356078</v>
       </c>
       <c r="B18" t="n">
-        <v>79810</v>
+        <v>79811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>130356107</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>130356201</v>
       </c>
       <c r="B20" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>130358819</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>130356560</v>
       </c>
       <c r="B22" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130356644</v>
       </c>
       <c r="B23" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>130609237</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>130607800</v>
       </c>
       <c r="B25" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>130609563</v>
       </c>
       <c r="B26" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>130608442</v>
       </c>
       <c r="B27" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>130607296</v>
       </c>
       <c r="B28" t="n">
-        <v>79252</v>
+        <v>79253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>130608573</v>
       </c>
       <c r="B29" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>130607874</v>
       </c>
       <c r="B30" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>130607970</v>
       </c>
       <c r="B31" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>130607960</v>
       </c>
       <c r="B32" t="n">
-        <v>92374</v>
+        <v>92375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>130608723</v>
       </c>
       <c r="B33" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>130609721</v>
       </c>
       <c r="B34" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>130608518</v>
       </c>
       <c r="B35" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>130606943</v>
       </c>
       <c r="B36" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356032</v>
+        <v>130356714</v>
       </c>
       <c r="B5" t="n">
-        <v>79811</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485321</v>
+        <v>485656</v>
       </c>
       <c r="R5" t="n">
-        <v>6939394</v>
+        <v>6939423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356714</v>
+        <v>130356032</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>79811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485656</v>
+        <v>485321</v>
       </c>
       <c r="R6" t="n">
-        <v>6939423</v>
+        <v>6939394</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1648,45 +1648,64 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B11" t="n">
-        <v>80326</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R11" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,64 +1774,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B12" t="n">
-        <v>57053</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R12" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356809</v>
+        <v>130356367</v>
       </c>
       <c r="B13" t="n">
-        <v>83193</v>
+        <v>78978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485662</v>
+        <v>485434</v>
       </c>
       <c r="R13" t="n">
-        <v>6939425</v>
+        <v>6939341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B14" t="n">
-        <v>78978</v>
+        <v>83193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R14" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4133,32 +4133,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130609721</v>
+        <v>130608518</v>
       </c>
       <c r="B34" t="n">
-        <v>80327</v>
+        <v>91739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485397</v>
+        <v>485649</v>
       </c>
       <c r="R34" t="n">
-        <v>6939386</v>
+        <v>6939253</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,32 +4240,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B35" t="n">
-        <v>91739</v>
+        <v>80327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R35" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1648,64 +1648,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130356574</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485605</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939402</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,45 +1755,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356521</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>57053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485552</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356367</v>
+        <v>130359609</v>
       </c>
       <c r="B13" t="n">
-        <v>78978</v>
+        <v>80327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485434</v>
+        <v>485646</v>
       </c>
       <c r="R13" t="n">
-        <v>6939341</v>
+        <v>6939616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130356809</v>
+        <v>130356367</v>
       </c>
       <c r="B14" t="n">
-        <v>83193</v>
+        <v>78978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485662</v>
+        <v>485434</v>
       </c>
       <c r="R14" t="n">
-        <v>6939425</v>
+        <v>6939341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130359609</v>
+        <v>130356809</v>
       </c>
       <c r="B15" t="n">
-        <v>80327</v>
+        <v>83193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485646</v>
+        <v>485662</v>
       </c>
       <c r="R15" t="n">
-        <v>6939616</v>
+        <v>6939425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4133,32 +4133,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B34" t="n">
-        <v>91739</v>
+        <v>80327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R34" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130609721</v>
+        <v>130606943</v>
       </c>
       <c r="B35" t="n">
-        <v>80327</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,34 +4251,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485397</v>
+        <v>485317</v>
       </c>
       <c r="R35" t="n">
-        <v>6939386</v>
+        <v>6939367</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4310,7 +4324,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4320,7 +4334,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4347,59 +4361,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130606943</v>
+        <v>130608518</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>91739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485317</v>
+        <v>485649</v>
       </c>
       <c r="R36" t="n">
-        <v>6939367</v>
+        <v>6939253</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130356174</v>
+        <v>130359584</v>
       </c>
       <c r="B8" t="n">
-        <v>92375</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485386</v>
+        <v>485661</v>
       </c>
       <c r="R8" t="n">
-        <v>6939403</v>
+        <v>6939645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130356421</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485464</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130356174</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>92375</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485386</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1621,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130356367</v>
+        <v>130356809</v>
       </c>
       <c r="B14" t="n">
-        <v>78978</v>
+        <v>83193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485434</v>
+        <v>485662</v>
       </c>
       <c r="R14" t="n">
-        <v>6939341</v>
+        <v>6939425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356809</v>
+        <v>130356367</v>
       </c>
       <c r="B15" t="n">
-        <v>83193</v>
+        <v>78978</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485662</v>
+        <v>485434</v>
       </c>
       <c r="R15" t="n">
-        <v>6939425</v>
+        <v>6939341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4240,59 +4240,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130606943</v>
+        <v>130608518</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>91739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485317</v>
+        <v>485649</v>
       </c>
       <c r="R35" t="n">
-        <v>6939367</v>
+        <v>6939253</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4310,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4334,7 +4320,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4361,45 +4347,59 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130608518</v>
+        <v>130606943</v>
       </c>
       <c r="B36" t="n">
-        <v>91739</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485649</v>
+        <v>485317</v>
       </c>
       <c r="R36" t="n">
-        <v>6939253</v>
+        <v>6939367</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130358340</v>
+        <v>130607296</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486167</v>
+        <v>485415</v>
       </c>
       <c r="R2" t="n">
-        <v>6939015</v>
+        <v>6939350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130359237</v>
+        <v>130356809</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486152</v>
+        <v>485662</v>
       </c>
       <c r="R3" t="n">
-        <v>6939430</v>
+        <v>6939425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130358664</v>
+        <v>130356174</v>
       </c>
       <c r="B4" t="n">
-        <v>78228</v>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486199</v>
+        <v>485386</v>
       </c>
       <c r="R4" t="n">
-        <v>6939172</v>
+        <v>6939403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130356714</v>
+        <v>130607960</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485656</v>
+        <v>485558</v>
       </c>
       <c r="R5" t="n">
-        <v>6939423</v>
+        <v>6939298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,22 +1066,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130356032</v>
+        <v>130358477</v>
       </c>
       <c r="B6" t="n">
-        <v>79811</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485321</v>
+        <v>486159</v>
       </c>
       <c r="R6" t="n">
-        <v>6939394</v>
+        <v>6939029</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130358477</v>
+        <v>130356648</v>
       </c>
       <c r="B7" t="n">
-        <v>83067</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486159</v>
+        <v>485635</v>
       </c>
       <c r="R7" t="n">
-        <v>6939029</v>
+        <v>6939414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130356174</v>
+        <v>130359609</v>
       </c>
       <c r="B8" t="n">
-        <v>92383</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485386</v>
+        <v>485646</v>
       </c>
       <c r="R8" t="n">
-        <v>6939403</v>
+        <v>6939616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130359584</v>
+        <v>130607800</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485661</v>
+        <v>485525</v>
       </c>
       <c r="R9" t="n">
-        <v>6939645</v>
+        <v>6939315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,22 +1494,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1524,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130356421</v>
+        <v>130609721</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485464</v>
+        <v>485397</v>
       </c>
       <c r="R10" t="n">
-        <v>6939338</v>
+        <v>6939386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,22 +1601,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,22 +1631,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130356521</v>
+        <v>130608518</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,53 +1654,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485552</v>
+        <v>485649</v>
       </c>
       <c r="R11" t="n">
-        <v>6939396</v>
+        <v>6939253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,22 +1708,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,44 +1738,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356574</v>
+        <v>130356107</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485605</v>
+        <v>485365</v>
       </c>
       <c r="R12" t="n">
-        <v>6939402</v>
+        <v>6939397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356367</v>
+        <v>130356421</v>
       </c>
       <c r="B13" t="n">
-        <v>78978</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485434</v>
+        <v>485464</v>
       </c>
       <c r="R13" t="n">
-        <v>6939341</v>
+        <v>6939338</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,45 +1964,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130359609</v>
+        <v>130358340</v>
       </c>
       <c r="B14" t="n">
-        <v>80327</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485646</v>
+        <v>486167</v>
       </c>
       <c r="R14" t="n">
-        <v>6939616</v>
+        <v>6939015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,45 +2071,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130356809</v>
+        <v>130358819</v>
       </c>
       <c r="B15" t="n">
-        <v>83193</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485662</v>
+        <v>486135</v>
       </c>
       <c r="R15" t="n">
-        <v>6939425</v>
+        <v>6939272</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,45 +2178,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130356648</v>
+        <v>130359237</v>
       </c>
       <c r="B16" t="n">
-        <v>80327</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485635</v>
+        <v>486152</v>
       </c>
       <c r="R16" t="n">
-        <v>6939414</v>
+        <v>6939430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2309,45 +2285,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130358621</v>
+        <v>130607708</v>
       </c>
       <c r="B17" t="n">
-        <v>78979</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486196</v>
+        <v>485501</v>
       </c>
       <c r="R17" t="n">
-        <v>6939161</v>
+        <v>6939298</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,22 +2350,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,44 +2380,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130356078</v>
+        <v>130608442</v>
       </c>
       <c r="B18" t="n">
-        <v>79811</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2451,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485335</v>
+        <v>485650</v>
       </c>
       <c r="R18" t="n">
-        <v>6939388</v>
+        <v>6939249</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,22 +2457,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,26 +2487,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130356107</v>
+        <v>130609237</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2558,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485365</v>
+        <v>485567</v>
       </c>
       <c r="R19" t="n">
-        <v>6939397</v>
+        <v>6939406</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,22 +2564,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,22 +2594,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130356201</v>
+        <v>130357350</v>
       </c>
       <c r="B20" t="n">
-        <v>80326</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2617,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485386</v>
+        <v>485779</v>
       </c>
       <c r="R20" t="n">
-        <v>6939403</v>
+        <v>6939306</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130358819</v>
+        <v>130356367</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,34 +2724,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486135</v>
+        <v>485434</v>
       </c>
       <c r="R21" t="n">
-        <v>6939272</v>
+        <v>6939341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130356560</v>
+        <v>130356201</v>
       </c>
       <c r="B22" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485605</v>
+        <v>485386</v>
       </c>
       <c r="R22" t="n">
-        <v>6939401</v>
+        <v>6939403</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2914,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2924,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130356644</v>
+        <v>130356560</v>
       </c>
       <c r="B23" t="n">
-        <v>80326</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485635</v>
+        <v>485605</v>
       </c>
       <c r="R23" t="n">
-        <v>6939414</v>
+        <v>6939401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3031,7 +3007,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130609237</v>
+        <v>130356574</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3093,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485567</v>
+        <v>485605</v>
       </c>
       <c r="R24" t="n">
-        <v>6939406</v>
+        <v>6939402</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,22 +3099,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3153,22 +3129,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130607800</v>
+        <v>130356644</v>
       </c>
       <c r="B25" t="n">
-        <v>80349</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485525</v>
+        <v>485635</v>
       </c>
       <c r="R25" t="n">
-        <v>6939315</v>
+        <v>6939414</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,22 +3206,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3260,22 +3236,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130609563</v>
+        <v>130356906</v>
       </c>
       <c r="B26" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485409</v>
+        <v>485679</v>
       </c>
       <c r="R26" t="n">
-        <v>6939407</v>
+        <v>6939384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,22 +3313,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3367,22 +3343,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130608442</v>
+        <v>130356940</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3390,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3414,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485650</v>
+        <v>485667</v>
       </c>
       <c r="R27" t="n">
-        <v>6939249</v>
+        <v>6939369</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,22 +3420,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,22 +3450,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130607296</v>
+        <v>130357215</v>
       </c>
       <c r="B28" t="n">
-        <v>79275</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,34 +3473,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485415</v>
+        <v>485765</v>
       </c>
       <c r="R28" t="n">
-        <v>6939350</v>
+        <v>6939316</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3551,22 +3527,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3581,22 +3557,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130608573</v>
+        <v>130357384</v>
       </c>
       <c r="B29" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,14 +3600,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485661</v>
+        <v>485781</v>
       </c>
       <c r="R29" t="n">
-        <v>6939262</v>
+        <v>6939306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,22 +3634,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,22 +3664,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130607874</v>
+        <v>130359584</v>
       </c>
       <c r="B30" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485546</v>
+        <v>485661</v>
       </c>
       <c r="R30" t="n">
-        <v>6939308</v>
+        <v>6939645</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,22 +3741,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3795,22 +3771,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130607970</v>
+        <v>130607874</v>
       </c>
       <c r="B31" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3842,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485558</v>
+        <v>485546</v>
       </c>
       <c r="R31" t="n">
-        <v>6939298</v>
+        <v>6939308</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3877,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3887,7 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3914,32 +3890,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130607960</v>
+        <v>130607970</v>
       </c>
       <c r="B32" t="n">
-        <v>92407</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,7 +3960,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3994,7 +3970,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4021,10 +3997,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130608723</v>
+        <v>130608573</v>
       </c>
       <c r="B33" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4056,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485644</v>
+        <v>485661</v>
       </c>
       <c r="R33" t="n">
-        <v>6939283</v>
+        <v>6939262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4091,7 +4067,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4101,12 +4077,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På grankvistar</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4133,10 +4104,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130606943</v>
+        <v>130608723</v>
       </c>
       <c r="B34" t="n">
-        <v>58043</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,48 +4115,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485317</v>
+        <v>485644</v>
       </c>
       <c r="R34" t="n">
-        <v>6939367</v>
+        <v>6939283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,7 +4174,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4227,7 +4184,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På grankvistar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,32 +4216,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130608518</v>
+        <v>130609563</v>
       </c>
       <c r="B35" t="n">
-        <v>91771</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4289,10 +4251,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485649</v>
+        <v>485409</v>
       </c>
       <c r="R35" t="n">
-        <v>6939253</v>
+        <v>6939407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,7 +4286,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4334,7 +4296,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4361,10 +4323,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130609721</v>
+        <v>130358664</v>
       </c>
       <c r="B36" t="n">
-        <v>80349</v>
+        <v>78334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,34 +4334,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485397</v>
+        <v>486199</v>
       </c>
       <c r="R36" t="n">
-        <v>6939386</v>
+        <v>6939172</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4426,22 +4388,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4456,15 +4418,807 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130356714</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>485656</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6939423</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130357698</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storfloberget, Storfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>485996</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6939270</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130356521</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>485552</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6939396</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130606943</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>485317</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6939367</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Erik Wilhelmsson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Erik Wilhelmsson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130358621</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storfloberget, Storfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>486196</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6939161</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130356032</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>485321</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6939394</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130356078</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>485335</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6939388</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130607296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130607960</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358477</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130359609</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130607800</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609721</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130608518</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356107</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356421</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358340</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358819</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130359237</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130607708</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130608442</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609237</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130357350</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356367</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356201</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356560</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,6 +3253,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356574</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356644</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3352,6 +3477,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356906</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3459,6 +3589,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356940</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130357215</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3673,6 +3813,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130357384</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3780,6 +3925,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130359584</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3887,6 +4037,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130607874</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3994,6 +4149,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130607970</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130608573</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4213,6 +4378,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130608723</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4320,6 +4490,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130609563</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4427,6 +4602,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358664</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4539,6 +4719,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356714</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4651,6 +4836,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130357698</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4777,6 +4967,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356521</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4898,6 +5093,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130606943</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5005,6 +5205,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358621</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5112,6 +5317,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356032</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5219,8 +5429,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356078</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57244-2025 artfynd.xlsx
+++ b/artfynd/A 57244-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,45 +904,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130356174</v>
+        <v>136553521</v>
       </c>
       <c r="B4" t="n">
-        <v>92509</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485386</v>
+        <v>485700</v>
       </c>
       <c r="R4" t="n">
-        <v>6939403</v>
+        <v>6939179</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,27 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med stora fruktkroppar</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,24 +989,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356174</t>
+          <t>https://artportalen.se/Sighting/136553521</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130607960</v>
+        <v>130356174</v>
       </c>
       <c r="B5" t="n">
         <v>92509</v>
@@ -1056,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485558</v>
+        <v>485386</v>
       </c>
       <c r="R5" t="n">
-        <v>6939298</v>
+        <v>6939403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,22 +1071,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med stora fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,62 +1106,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130607960</t>
+          <t>https://artportalen.se/Sighting/130356174</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130358477</v>
+        <v>130607960</v>
       </c>
       <c r="B6" t="n">
-        <v>83173</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486159</v>
+        <v>485558</v>
       </c>
       <c r="R6" t="n">
-        <v>6939029</v>
+        <v>6939298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1218,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130358477</t>
+          <t>https://artportalen.se/Sighting/130607960</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130356648</v>
+        <v>130358477</v>
       </c>
       <c r="B7" t="n">
-        <v>80433</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,34 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485635</v>
+        <v>486159</v>
       </c>
       <c r="R7" t="n">
-        <v>6939414</v>
+        <v>6939029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,13 +1341,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356648</t>
+          <t>https://artportalen.se/Sighting/130358477</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130359609</v>
+        <v>130356648</v>
       </c>
       <c r="B8" t="n">
         <v>80433</v>
@@ -1392,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485646</v>
+        <v>485635</v>
       </c>
       <c r="R8" t="n">
-        <v>6939616</v>
+        <v>6939414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,13 +1453,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130359609</t>
+          <t>https://artportalen.se/Sighting/130356648</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130607800</v>
+        <v>130359609</v>
       </c>
       <c r="B9" t="n">
         <v>80433</v>
@@ -1504,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485525</v>
+        <v>485646</v>
       </c>
       <c r="R9" t="n">
-        <v>6939315</v>
+        <v>6939616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,22 +1524,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,24 +1554,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130607800</t>
+          <t>https://artportalen.se/Sighting/130359609</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130609721</v>
+        <v>130607800</v>
       </c>
       <c r="B10" t="n">
         <v>80433</v>
@@ -1616,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485397</v>
+        <v>485525</v>
       </c>
       <c r="R10" t="n">
-        <v>6939386</v>
+        <v>6939315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,38 +1677,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130609721</t>
+          <t>https://artportalen.se/Sighting/130607800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130608518</v>
+        <v>130609721</v>
       </c>
       <c r="B11" t="n">
-        <v>91872</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485649</v>
+        <v>485397</v>
       </c>
       <c r="R11" t="n">
-        <v>6939253</v>
+        <v>6939386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,51 +1789,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130608518</t>
+          <t>https://artportalen.se/Sighting/130609721</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130356107</v>
+        <v>136553688</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>93400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485365</v>
+        <v>485710</v>
       </c>
       <c r="R12" t="n">
-        <v>6939397</v>
+        <v>6939166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,22 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,49 +1880,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356107</t>
+          <t>https://artportalen.se/Sighting/136553688</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130356421</v>
+        <v>130608518</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485464</v>
+        <v>485649</v>
       </c>
       <c r="R13" t="n">
-        <v>6939338</v>
+        <v>6939253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,22 +1962,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,24 +1992,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356421</t>
+          <t>https://artportalen.se/Sighting/130608518</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130358340</v>
+        <v>130356107</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2060,14 +2040,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486167</v>
+        <v>485365</v>
       </c>
       <c r="R14" t="n">
-        <v>6939015</v>
+        <v>6939397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,13 +2115,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130358340</t>
+          <t>https://artportalen.se/Sighting/130356107</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130358819</v>
+        <v>130356421</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2172,14 +2152,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486135</v>
+        <v>485464</v>
       </c>
       <c r="R15" t="n">
-        <v>6939272</v>
+        <v>6939338</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,13 +2227,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130358819</t>
+          <t>https://artportalen.se/Sighting/130356421</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130359237</v>
+        <v>130358340</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2288,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486152</v>
+        <v>486167</v>
       </c>
       <c r="R16" t="n">
-        <v>6939430</v>
+        <v>6939015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,13 +2339,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130359237</t>
+          <t>https://artportalen.se/Sighting/130358340</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130607708</v>
+        <v>130358819</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2396,14 +2376,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485501</v>
+        <v>486135</v>
       </c>
       <c r="R17" t="n">
-        <v>6939298</v>
+        <v>6939272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,22 +2410,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,24 +2440,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130607708</t>
+          <t>https://artportalen.se/Sighting/130358819</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130608442</v>
+        <v>130359237</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2508,14 +2488,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485650</v>
+        <v>486152</v>
       </c>
       <c r="R18" t="n">
-        <v>6939249</v>
+        <v>6939430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,22 +2522,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,24 +2552,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130608442</t>
+          <t>https://artportalen.se/Sighting/130359237</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130609237</v>
+        <v>130607708</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2624,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485567</v>
+        <v>485501</v>
       </c>
       <c r="R19" t="n">
-        <v>6939406</v>
+        <v>6939298</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,51 +2675,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130609237</t>
+          <t>https://artportalen.se/Sighting/130607708</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130357350</v>
+        <v>130608442</v>
       </c>
       <c r="B20" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485779</v>
+        <v>485650</v>
       </c>
       <c r="R20" t="n">
-        <v>6939306</v>
+        <v>6939249</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,22 +2746,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,49 +2776,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130357350</t>
+          <t>https://artportalen.se/Sighting/130608442</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130356367</v>
+        <v>130609237</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485434</v>
+        <v>485567</v>
       </c>
       <c r="R21" t="n">
-        <v>6939341</v>
+        <v>6939406</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,22 +2858,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,27 +2888,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356367</t>
+          <t>https://artportalen.se/Sighting/130609237</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130356201</v>
+        <v>130357350</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,34 +2916,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485386</v>
+        <v>485779</v>
       </c>
       <c r="R22" t="n">
-        <v>6939403</v>
+        <v>6939306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2995,7 +2975,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +2985,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,16 +3011,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356201</t>
+          <t>https://artportalen.se/Sighting/130357350</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130356560</v>
+        <v>130356367</v>
       </c>
       <c r="B23" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,21 +3028,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485605</v>
+        <v>485434</v>
       </c>
       <c r="R23" t="n">
-        <v>6939401</v>
+        <v>6939341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3107,7 +3087,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3097,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,13 +3123,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356560</t>
+          <t>https://artportalen.se/Sighting/130356367</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130356574</v>
+        <v>130356201</v>
       </c>
       <c r="B24" t="n">
         <v>80432</v>
@@ -3184,10 +3164,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485605</v>
+        <v>485386</v>
       </c>
       <c r="R24" t="n">
-        <v>6939402</v>
+        <v>6939403</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3219,7 +3199,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3209,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,13 +3235,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356574</t>
+          <t>https://artportalen.se/Sighting/130356201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130356644</v>
+        <v>130356560</v>
       </c>
       <c r="B25" t="n">
         <v>80432</v>
@@ -3296,10 +3276,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485635</v>
+        <v>485605</v>
       </c>
       <c r="R25" t="n">
-        <v>6939414</v>
+        <v>6939401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3311,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3321,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,13 +3347,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356644</t>
+          <t>https://artportalen.se/Sighting/130356560</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130356906</v>
+        <v>130356574</v>
       </c>
       <c r="B26" t="n">
         <v>80432</v>
@@ -3408,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>485679</v>
+        <v>485605</v>
       </c>
       <c r="R26" t="n">
-        <v>6939384</v>
+        <v>6939402</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,13 +3459,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356906</t>
+          <t>https://artportalen.se/Sighting/130356574</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130356940</v>
+        <v>130356644</v>
       </c>
       <c r="B27" t="n">
         <v>80432</v>
@@ -3520,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485667</v>
+        <v>485635</v>
       </c>
       <c r="R27" t="n">
-        <v>6939369</v>
+        <v>6939414</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3555,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,7 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,13 +3571,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356940</t>
+          <t>https://artportalen.se/Sighting/130356644</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130357215</v>
+        <v>130356906</v>
       </c>
       <c r="B28" t="n">
         <v>80432</v>
@@ -3628,14 +3608,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>485765</v>
+        <v>485679</v>
       </c>
       <c r="R28" t="n">
-        <v>6939316</v>
+        <v>6939384</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,7 +3647,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3657,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,13 +3683,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130357215</t>
+          <t>https://artportalen.se/Sighting/130356906</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130357384</v>
+        <v>130356940</v>
       </c>
       <c r="B29" t="n">
         <v>80432</v>
@@ -3740,14 +3720,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485781</v>
+        <v>485667</v>
       </c>
       <c r="R29" t="n">
-        <v>6939306</v>
+        <v>6939369</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3779,7 +3759,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3769,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,13 +3795,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130357384</t>
+          <t>https://artportalen.se/Sighting/130356940</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130359584</v>
+        <v>130357215</v>
       </c>
       <c r="B30" t="n">
         <v>80432</v>
@@ -3852,14 +3832,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485661</v>
+        <v>485765</v>
       </c>
       <c r="R30" t="n">
-        <v>6939645</v>
+        <v>6939316</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3891,7 +3871,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3881,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,13 +3907,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130359584</t>
+          <t>https://artportalen.se/Sighting/130357215</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130607874</v>
+        <v>130357384</v>
       </c>
       <c r="B31" t="n">
         <v>80432</v>
@@ -3964,14 +3944,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485546</v>
+        <v>485781</v>
       </c>
       <c r="R31" t="n">
-        <v>6939308</v>
+        <v>6939306</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3998,22 +3978,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4028,24 +4008,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130607874</t>
+          <t>https://artportalen.se/Sighting/130357384</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130607970</v>
+        <v>130359584</v>
       </c>
       <c r="B32" t="n">
         <v>80432</v>
@@ -4080,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485558</v>
+        <v>485661</v>
       </c>
       <c r="R32" t="n">
-        <v>6939298</v>
+        <v>6939645</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4110,22 +4090,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4140,24 +4120,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130607970</t>
+          <t>https://artportalen.se/Sighting/130359584</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130608573</v>
+        <v>130607874</v>
       </c>
       <c r="B33" t="n">
         <v>80432</v>
@@ -4192,10 +4172,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>485661</v>
+        <v>485546</v>
       </c>
       <c r="R33" t="n">
-        <v>6939262</v>
+        <v>6939308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4227,7 +4207,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,7 +4217,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,13 +4243,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130608573</t>
+          <t>https://artportalen.se/Sighting/130607874</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130608723</v>
+        <v>130607970</v>
       </c>
       <c r="B34" t="n">
         <v>80432</v>
@@ -4304,10 +4284,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485644</v>
+        <v>485558</v>
       </c>
       <c r="R34" t="n">
-        <v>6939283</v>
+        <v>6939298</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4339,7 +4319,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,12 +4329,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På grankvistar</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,13 +4355,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130608723</t>
+          <t>https://artportalen.se/Sighting/130607970</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130609563</v>
+        <v>130608573</v>
       </c>
       <c r="B35" t="n">
         <v>80432</v>
@@ -4421,10 +4396,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>485409</v>
+        <v>485661</v>
       </c>
       <c r="R35" t="n">
-        <v>6939407</v>
+        <v>6939262</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,7 +4431,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4441,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,16 +4467,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130609563</t>
+          <t>https://artportalen.se/Sighting/130608573</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130358664</v>
+        <v>130608723</v>
       </c>
       <c r="B36" t="n">
-        <v>78334</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4509,34 +4484,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486199</v>
+        <v>485644</v>
       </c>
       <c r="R36" t="n">
-        <v>6939172</v>
+        <v>6939283</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4563,22 +4538,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På grankvistar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,67 +4573,62 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130358664</t>
+          <t>https://artportalen.se/Sighting/130608723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130356714</v>
+        <v>130609563</v>
       </c>
       <c r="B37" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485656</v>
+        <v>485409</v>
       </c>
       <c r="R37" t="n">
-        <v>6939423</v>
+        <v>6939407</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4680,22 +4655,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4710,67 +4685,62 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356714</t>
+          <t>https://artportalen.se/Sighting/130609563</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130357698</v>
+        <v>130358664</v>
       </c>
       <c r="B38" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>485996</v>
+        <v>486199</v>
       </c>
       <c r="R38" t="n">
-        <v>6939270</v>
+        <v>6939172</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4802,7 +4772,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,7 +4782,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,16 +4808,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130357698</t>
+          <t>https://artportalen.se/Sighting/130358664</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130356521</v>
+        <v>130356714</v>
       </c>
       <c r="B39" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4855,41 +4825,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4898,10 +4854,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485552</v>
+        <v>485656</v>
       </c>
       <c r="R39" t="n">
-        <v>6939396</v>
+        <v>6939423</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4933,7 +4889,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,7 +4899,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4969,65 +4925,56 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356521</t>
+          <t>https://artportalen.se/Sighting/130356714</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130606943</v>
+        <v>130357698</v>
       </c>
       <c r="B40" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485317</v>
+        <v>485996</v>
       </c>
       <c r="R40" t="n">
-        <v>6939367</v>
+        <v>6939270</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5054,22 +5001,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,62 +5031,81 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Gillhovs Skogsgrupp</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130606943</t>
+          <t>https://artportalen.se/Sighting/130357698</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130358621</v>
+        <v>130356521</v>
       </c>
       <c r="B41" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storfloberget, Storfloberget, Jmt</t>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486196</v>
+        <v>485552</v>
       </c>
       <c r="R41" t="n">
-        <v>6939161</v>
+        <v>6939396</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5171,7 +5137,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5181,7 +5147,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5207,16 +5173,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130358621</t>
+          <t>https://artportalen.se/Sighting/130356521</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130356032</v>
+        <v>130606943</v>
       </c>
       <c r="B42" t="n">
-        <v>79917</v>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,34 +5190,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ryflodalen, Ryflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>485321</v>
+        <v>485317</v>
       </c>
       <c r="R42" t="n">
-        <v>6939394</v>
+        <v>6939367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5278,22 +5258,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5308,27 +5288,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Gillhovs Skogsgrupp</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130356032</t>
+          <t>https://artportalen.se/Sighting/130606943</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130356078</v>
+        <v>130358621</v>
       </c>
       <c r="B43" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,34 +5316,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ryflodalen, Ryflodalen, Jmt</t>
+          <t>Storfloberget, Storfloberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485335</v>
+        <v>486196</v>
       </c>
       <c r="R43" t="n">
-        <v>6939388</v>
+        <v>6939161</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5395,7 +5375,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5405,7 +5385,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5430,6 +5410,230 @@
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130358621</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130356032</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>485321</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6939394</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130356032</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130356078</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ryflodalen, Ryflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>485335</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6939388</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Gillhovs Skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130356078</t>
         </is>
@@ -5479,6 +5683,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
